--- a/file/qs-10.xlsx
+++ b/file/qs-10.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B72"/>
+  <dimension ref="A1:B79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,852 +431,936 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>002653</t>
+          <t>603500</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>海思科</t>
+          <t>祥和实业</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>600988</t>
+          <t>002774</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>赤峰黄金</t>
+          <t>快意电梯</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>002294</t>
+          <t>002692</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>信立泰</t>
+          <t>远程股份</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>600547</t>
+          <t>002998</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>山东黄金</t>
+          <t>优彩资源</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>001914</t>
+          <t>002877</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>招商积余</t>
+          <t>智能自控</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>002891</t>
+          <t>002441</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>中宠股份</t>
+          <t>众业达</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>000975</t>
+          <t>000421</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>山金国际</t>
+          <t>南京公用</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>300398</t>
+          <t>002442</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>飞凯材料</t>
+          <t>龙星科技</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>000573</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>渝农商行</t>
+          <t>粤宏远Ａ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>002675</t>
+          <t>002787</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>东诚药业</t>
+          <t>华源控股</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>601288</t>
+          <t>002660</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>农业银行</t>
+          <t>茂硕电源</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>601328</t>
+          <t>002811</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>XD交通银</t>
+          <t>郑中设计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>600861</t>
+          <t>002674</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>北京人力</t>
+          <t>兴业科技</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>601988</t>
+          <t>002282</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>中国银行</t>
+          <t>博深股份</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>601398</t>
+          <t>002328</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>工商银行</t>
+          <t>新朋股份</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>600535</t>
+          <t>605001</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>天士力</t>
+          <t>威奥股份</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>600422</t>
+          <t>603177</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>昆药集团</t>
+          <t>德创环保</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>601939</t>
+          <t>603058</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>建设银行</t>
+          <t>永吉股份</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>600323</t>
+          <t>000530</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>瀚蓝环境</t>
+          <t>冰山冷热</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>600377</t>
+          <t>603617</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>宁沪高速</t>
+          <t>君禾股份</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>002690</t>
+          <t>600854</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>美亚光电</t>
+          <t>春兰股份</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>603128</t>
+          <t>002012</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>华贸物流</t>
+          <t>凯恩股份</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>600795</t>
+          <t>603012</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>国电电力</t>
+          <t>创力集团</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>600406</t>
+          <t>603332</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>国电南瑞</t>
+          <t>苏州龙杰</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>003006</t>
+          <t>002614</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>百亚股份</t>
+          <t>奥佳华</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>600025</t>
+          <t>002887</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>华能水电</t>
+          <t>绿茵生态</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>601169</t>
+          <t>002337</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>北京银行</t>
+          <t>赛象科技</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>603939</t>
+          <t>000570</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>益丰药房</t>
+          <t>苏常柴Ａ</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>600285</t>
+          <t>600796</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>羚锐制药</t>
+          <t>钱江生化</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>601825</t>
+          <t>603135</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>沪农商行</t>
+          <t>中重科技</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>603288</t>
+          <t>002350</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>海天味业</t>
+          <t>北京科锐</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>000598</t>
+          <t>603601</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>兴蓉环境</t>
+          <t>再升科技</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>600863</t>
+          <t>605500</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>内蒙华电</t>
+          <t>森林包装</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>002299</t>
+          <t>002593</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>圣农发展</t>
+          <t>日上集团</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>002410</t>
+          <t>002686</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>广联达</t>
+          <t>亿利达</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>600905</t>
+          <t>002560</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>三峡能源</t>
+          <t>通达股份</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>603317</t>
+          <t>002451</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>天味食品</t>
+          <t>摩恩电气</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>601107</t>
+          <t>603808</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>四川成渝</t>
+          <t>歌力思</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>600033</t>
+          <t>603017</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>福建高速</t>
+          <t>中衡设计</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>603565</t>
+          <t>002598</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>中谷物流</t>
+          <t>山东章鼓</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>601009</t>
+          <t>603725</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>南京银行</t>
+          <t>天安新材</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>600886</t>
+          <t>600630</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>国投电力</t>
+          <t>龙头股份</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>600461</t>
+          <t>600512</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>洪城环境</t>
+          <t>腾达建设</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>000999</t>
+          <t>002728</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>华润三九</t>
+          <t>特一药业</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>600919</t>
+          <t>002551</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>江苏银行</t>
+          <t>尚荣医疗</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>601963</t>
+          <t>002398</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>重庆银行</t>
+          <t>垒知集团</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>600011</t>
+          <t>002357</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>华能国际</t>
+          <t>富临运业</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>600887</t>
+          <t>002303</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>伊利股份</t>
+          <t>美盈森</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>000791</t>
+          <t>600356</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>甘肃能源</t>
+          <t>恒丰纸业</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>600873</t>
+          <t>002763</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>梅花生物</t>
+          <t>汇洁股份</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>600642</t>
+          <t>002817</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>申能股份</t>
+          <t>黄山胶囊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>002557</t>
+          <t>002753</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>洽洽食品</t>
+          <t>永东股份</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>300144</t>
+          <t>603811</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>宋城演艺</t>
+          <t>诚意药业</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>300783</t>
+          <t>605268</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>三只松鼠</t>
+          <t>王力安防</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>601229</t>
+          <t>002615</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>上海银行</t>
+          <t>哈尔斯</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>000600</t>
+          <t>000407</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>建投能源</t>
+          <t>胜利股份</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>000966</t>
+          <t>002443</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>长源电力</t>
+          <t>金洲管道</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>603156</t>
+          <t>603022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>养元饮品</t>
+          <t>新通联</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>603983</t>
+          <t>000548</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>丸美生物</t>
+          <t>湖南投资</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>601816</t>
+          <t>600379</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>京沪高铁</t>
+          <t>宝光股份</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>601595</t>
+          <t>600527</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>上海电影</t>
+          <t>江南高纤</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>603919</t>
+          <t>600638</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>金徽酒</t>
+          <t>新黄浦</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>002287</t>
+          <t>002783</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>奇正藏药</t>
+          <t>凯龙股份</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>002714</t>
+          <t>603797</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>牧原股份</t>
+          <t>联泰环保</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>601088</t>
+          <t>600222</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>中国神华</t>
+          <t>太龙药业</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>600729</t>
+          <t>603331</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>重庆百货</t>
+          <t>百达精工</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>600866</t>
+          <t>600526</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>星湖科技</t>
+          <t>菲达环保</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>000899</t>
+          <t>603987</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>赣能股份</t>
+          <t>康德莱</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>600258</t>
+          <t>002788</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>首旅酒店</t>
+          <t>鹭燕医药</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>600827</t>
+          <t>603817</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>百联股份</t>
+          <t>海峡环保</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>600746</t>
+          <t>000705</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>江苏索普</t>
+          <t>浙江震元</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>600097</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>开创国际</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>600620</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>天宸股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>002224</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>三 力 士</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>603318</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>水发燃气</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>605169</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>洪通燃气</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>002852</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>道道全</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>002404</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>嘉欣丝绸</t>
         </is>
       </c>
     </row>
